--- a/survey_templates/050_corporate_sustainability_maturity_survey--survey_templates.xlsx
+++ b/survey_templates/050_corporate_sustainability_maturity_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -561,161 +561,189 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>domain_page</t>
+          <t>sustainability_management_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Sustainability Management</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Describe your approach to sustainability management.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>maturity_level_page</t>
+          <t>human_rights_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maturity Level</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Human Rights</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How important is human rights in the company's operations?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>challenges_page</t>
+          <t>environmental_impact_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Challenges</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Environmental Impact</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>How does the company measure its environmental impact?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>challenges_page</t>
+          <t>stakeholder_engagement_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Challenges</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Stakeholder Engagement</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How does the company engage with stakeholders to promote transparency and accountability?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>challenges_page</t>
+          <t>social_ethics_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Challenges</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Social and Ethical</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What are the company's key social and ethical priorities?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>introduction_page</t>
+          <t>community_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How does the company contribute to the well-being of local communities?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>conclusion_page</t>
+          <t>challenges_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Conclusion</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Challenges</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>What are some of the main challenges the company faces in achieving its sustainability goals?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -738,24 +766,24 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submission_page</t>
+          <t>conclusion_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Conclusion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -779,9 +807,9 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,221 +832,221 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>human_rights_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1:_sustainability_management</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1: Sustainability Management</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>human_rights_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2:_human_rights</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2: Human Rights</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>human_rights_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3:_environmental_impact</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3: Environmental Impact</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>human_rights_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4:_stakeholder_engagement</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4: Stakeholder Engagement</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>environmental_impact_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5:_social_and_ethical</t>
+          <t>greenhouse_gas_emissions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5: Social and Ethical</t>
+          <t>Greenhouse Gas Emissions</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>domain_page_choices</t>
+          <t>environmental_impact_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6:_community</t>
+          <t>water_usage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6: Community</t>
+          <t>Water Usage</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>maturity_level_page_choices</t>
+          <t>environmental_impact_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1:_high</t>
+          <t>energy_consumption</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1: High</t>
+          <t>Energy Consumption</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>maturity_level_page_choices</t>
+          <t>environmental_impact_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2:_medium</t>
+          <t>waste_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2: Medium</t>
+          <t>Waste Management</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>maturity_level_page_choices</t>
+          <t>environmental_impact_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3:_low</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3: Low</t>
+          <t>Recycling</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>maturity_level_page_choices</t>
+          <t>social_ethics_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4:_not_applicable</t>
+          <t>diversity_and_inclusion</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4: Not Applicable</t>
+          <t>Diversity and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>challenges_page_choices</t>
+          <t>social_ethics_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1:_lack_of_clear_objectives</t>
+          <t>human_rights</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1: Lack of clear objectives</t>
+          <t>Human Rights</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>challenges_page_choices</t>
+          <t>social_ethics_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2:_limited_resources</t>
+          <t>fair_labor_practices</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2: Limited resources</t>
+          <t>Fair Labor Practices</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>challenges_page_choices</t>
+          <t>social_ethics_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3:_lack_of_clear_policies</t>
+          <t>supply_chain_responsibility</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3: Lack of clear policies</t>
+          <t>Supply Chain Responsibility</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1058,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4:_lack_of_clear_communication</t>
+          <t>lack_of_clear_objectives</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4: Lack of clear communication</t>
+          <t>Lack of clear objectives</t>
         </is>
       </c>
     </row>
@@ -1047,63 +1075,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5:_lack_of_clear_metrics</t>
+          <t>limited_resources</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5: Lack of clear metrics</t>
+          <t>Limited resources</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submission_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1:_submit</t>
+          <t>lack_of_clear_policies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1: Submit</t>
+          <t>Lack of clear policies</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>submission_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2:_save_draft</t>
+          <t>lack_of_clear_communication</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2: Save Draft</t>
+          <t>Lack of clear communication</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submission_page_choices</t>
+          <t>challenges_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3:_cancel</t>
+          <t>lack_of_clear_metrics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3: Cancel</t>
+          <t>Lack of clear metrics</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1143,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1:_submit</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1: Submit</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1160,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2:_save_draft</t>
+          <t>save_draft</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2: Save Draft</t>
+          <t>Save Draft</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1177,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3:_cancel</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3: Cancel</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
